--- a/App/TestCases_App/User_gerente.xlsx
+++ b/App/TestCases_App/User_gerente.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\App\TestCases_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6C73085-F021-4141-8E4A-43BAB447D5B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26F463D1-6091-4E17-9905-02E95A31421D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="132">
   <si>
     <t>Num</t>
   </si>
@@ -44,9 +44,6 @@
   </si>
   <si>
     <t>Notes</t>
-  </si>
-  <si>
-    <t>Views of tables</t>
   </si>
   <si>
     <t>Tickets' history</t>
@@ -138,9 +135,6 @@
     <t>OK</t>
   </si>
   <si>
-    <t>Se ha introducido un número desorbitado de comensales, y al ir a pagar, se ha cerrado la aplicación.</t>
-  </si>
-  <si>
     <t>BL</t>
   </si>
   <si>
@@ -249,9 +243,6 @@
     <t>1. The operation is done</t>
   </si>
   <si>
-    <t>ok</t>
-  </si>
-  <si>
     <t>El botón "MODO TPV" pisotea la barra superior. Waiter001.jpg</t>
   </si>
   <si>
@@ -352,9 +343,6 @@
     <t>USERMAN002</t>
   </si>
   <si>
-    <t>USERMAN003</t>
-  </si>
-  <si>
     <t>USERMAN004</t>
   </si>
   <si>
@@ -439,14 +427,59 @@
     <t>Manager user page home</t>
   </si>
   <si>
-    <t xml:space="preserve">1. The user sees the manager page home
+    <t>El menu sale cortado: Waiter002.jpg</t>
+  </si>
+  <si>
+    <t>1. The user is logged
+2. The manager page home is correctly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user clicks his pin,clicks "Acceder"
+2.The user sees the manager page home
 </t>
   </si>
   <si>
-    <t>1. The manager page home is correctly.</t>
-  </si>
-  <si>
-    <t>El menu sale cortado: Waiter002.jpg</t>
+    <t>Change user: Cancel</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Cambiar de usuario"
+2. The user clicks the back arrow</t>
+  </si>
+  <si>
+    <t>1. The user does not change of user.</t>
+  </si>
+  <si>
+    <t>Change the restaurant</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Cambiar de usuario"
+2. The user clicks the back arrow
+3. The user selects a restaurant.</t>
+  </si>
+  <si>
+    <t>1. The restaurant is changed.</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Cambiar de usuario"
+2. The user clicks the back arrow
+3. The user selects a restaurant.
+4. The user writes the pin</t>
+  </si>
+  <si>
+    <t>Change the restaurant with a wrong pin</t>
+  </si>
+  <si>
+    <t>Change the restaurant with a pin</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Cambiar de usuario"
+2. The user clicks the back arrow
+3. The user selects a restaurant.
+4. The user writes a wrong pin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. A message is shown
+</t>
   </si>
 </sst>
 </file>
@@ -921,7 +954,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="5"/>
@@ -960,28 +993,28 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -989,382 +1022,398 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
+        <v>121</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>123</v>
+      </c>
       <c r="G4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>31</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>65</v>
+        <v>124</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>78</v>
+        <v>125</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F5" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>126</v>
+      </c>
       <c r="G5" s="2" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>79</v>
+        <v>127</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F6" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>126</v>
+      </c>
       <c r="G6" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H6" s="3"/>
     </row>
-    <row r="7" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>87</v>
+        <v>128</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F7" s="1"/>
+        <v>131</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="G7" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="2" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>88</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="F9" s="1"/>
       <c r="G9" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H9" s="3"/>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F12" s="1"/>
+        <v>85</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="G12" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
+        <v>45</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="F13" s="1"/>
       <c r="G13" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="1"/>
+        <v>66</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F14" s="1"/>
       <c r="G14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
         <v>11</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>14</v>
-      </c>
       <c r="B15" s="1" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="F15" s="1"/>
       <c r="G15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>17</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>13</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <v>16</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H17" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H18" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="19" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H19" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="20" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>24</v>
@@ -1378,237 +1427,297 @@
     </row>
     <row r="21" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H21" s="3" t="s">
         <v>29</v>
       </c>
+      <c r="H21" s="3"/>
     </row>
     <row r="22" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>37</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>38</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="H22" s="3"/>
     </row>
     <row r="23" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>35</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
       <c r="G23" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H23" s="3"/>
     </row>
     <row r="24" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>42</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H25" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>22</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H26" s="3"/>
+    </row>
+    <row r="27" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>23</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F27" s="1"/>
+      <c r="G27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>24</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <v>25</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H26" s="3"/>
-    </row>
-    <row r="27" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
-        <v>26</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="3"/>
-    </row>
-    <row r="28" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
-        <v>27</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
+      <c r="D28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="F28" s="1"/>
       <c r="G28" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H28" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C29" s="1"/>
+        <v>111</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
-      <c r="G29" s="2"/>
+      <c r="G29" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="H29" s="3"/>
     </row>
-    <row r="30" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="3"/>
+    </row>
+    <row r="31" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>59</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="2" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="H31" s="3"/>
+    </row>
+    <row r="32" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>28</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="3"/>
+    </row>
+    <row r="33" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>29</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>30</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F34" s="1"/>
+      <c r="G34" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H34" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G29">
+  <conditionalFormatting sqref="G2:G32">
     <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>
@@ -1622,18 +1731,18 @@
       <formula>NOT(ISERROR(SEARCH("OK",G2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G30:G31">
+  <conditionalFormatting sqref="G33:G34">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
-      <formula>NOT(ISERROR(SEARCH("PTE",G30)))</formula>
+      <formula>NOT(ISERROR(SEARCH("PTE",G33)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="BL">
-      <formula>NOT(ISERROR(SEARCH("BL",G30)))</formula>
+      <formula>NOT(ISERROR(SEARCH("BL",G33)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="KO">
-      <formula>NOT(ISERROR(SEARCH("KO",G30)))</formula>
+      <formula>NOT(ISERROR(SEARCH("KO",G33)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="OK">
-      <formula>NOT(ISERROR(SEARCH("OK",G30)))</formula>
+      <formula>NOT(ISERROR(SEARCH("OK",G33)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/App/TestCases_App/User_gerente.xlsx
+++ b/App/TestCases_App/User_gerente.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\App\TestCases_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26F463D1-6091-4E17-9905-02E95A31421D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB0DC09-C877-4F3B-AED8-0B99146B24BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="138">
   <si>
     <t>Num</t>
   </si>
@@ -60,12 +60,6 @@
 3. Clicks "Cerrar mesa"</t>
   </si>
   <si>
-    <t>1. Select numbers of people
-2. Select several products
-3. Join table
-4. Clicks "Cerrar mesa"</t>
-  </si>
-  <si>
     <t>Take order: Join table</t>
   </si>
   <si>
@@ -75,34 +69,16 @@
     <t>Take order: Fee</t>
   </si>
   <si>
-    <t>1. Select numbers of people
-2. Select several products
-3. Add fee
-4. Clicks "Cerrar mesa"</t>
-  </si>
-  <si>
     <t>Take order: change type of menu</t>
   </si>
   <si>
     <t>Take order: find a product</t>
   </si>
   <si>
-    <t>1. Select numbers of people
-2. Select find product
-3. Add product
-4. Clicks "Cerrar mesa"</t>
-  </si>
-  <si>
     <t>Take order: Add modifiers</t>
   </si>
   <si>
     <t>Take order: Add modifiers, cancel</t>
-  </si>
-  <si>
-    <t>1. Select numbers of people
-2. Select a product
-3. Add a modifier, clicks "Añadir al pedido"
-4. Clicks "Cerrar mesa"</t>
   </si>
   <si>
     <t>1. Select numbers of people
@@ -111,12 +87,6 @@
 4. Clicks "Cerrar mesa"</t>
   </si>
   <si>
-    <t>1. Select numbers of people
-2. Select several products with his modifiers
-3. Select menu
-4. Clicks "Cerrar mesa"</t>
-  </si>
-  <si>
     <t>Con cada producto añadido, se está añadiendo el suplemento de terraza. Waiter003.jpg</t>
   </si>
   <si>
@@ -129,9 +99,6 @@
 4. Clicks "Cerrar mesa"</t>
   </si>
   <si>
-    <t>Se reparte la cuenta entre ocho, se hace un pago en efectivo, se hace un pago con tarjeta, pero al pagar el resto de la cuenta indica, se ha pagado 1/8 cuando han sido 2/8. Waiter004.jpg</t>
-  </si>
-  <si>
     <t>OK</t>
   </si>
   <si>
@@ -480,6 +447,58 @@
   <si>
     <t xml:space="preserve">1. A message is shown
 </t>
+  </si>
+  <si>
+    <t>Se reparte la cuenta entre ocho, se hace un pago en efectivo, se hace un pago con tarjeta, pero al pagar el resto de la cuenta indica, se ha pagado 1/8 cuando han sido 2/8. Waiter004.jpg  
+15/05/26, se hace un pedido para 6 personas, al ir a pagar da error: PED004.jpg</t>
+  </si>
+  <si>
+    <t>1.The user paid the bill.</t>
+  </si>
+  <si>
+    <t>The modifiers are added</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Select numbers of people
+2. Select a product
+3. Add a modifier, clicks "Añadir al pedido"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Select numbers of people
+2. Select find product
+3. Add product
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Select numbers of people
+2. Select several products with his modifiers
+3. Select menu
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Select numbers of people
+2. Select several products
+3. Add fee
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Select numbers of people
+2. Select several products
+3. Join table
+</t>
+  </si>
+  <si>
+    <t>1. The tables are joined.</t>
+  </si>
+  <si>
+    <t>1. The fee is added.</t>
+  </si>
+  <si>
+    <t>1. The menu is changed</t>
+  </si>
+  <si>
+    <t>1. The product is found.</t>
   </si>
 </sst>
 </file>
@@ -588,38 +607,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6565"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -998,23 +986,23 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -1022,22 +1010,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H3" s="3"/>
     </row>
@@ -1046,22 +1034,22 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H4" s="3"/>
     </row>
@@ -1070,22 +1058,22 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H5" s="3"/>
     </row>
@@ -1094,22 +1082,22 @@
         <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H6" s="3"/>
     </row>
@@ -1118,22 +1106,22 @@
         <v>2</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H7" s="3"/>
     </row>
@@ -1142,20 +1130,20 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H8" s="3"/>
     </row>
@@ -1164,20 +1152,22 @@
         <v>5</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F9" s="1"/>
+      <c r="F9" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="G9" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H9" s="3"/>
     </row>
@@ -1186,20 +1176,22 @@
         <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F10" s="1"/>
+        <v>75</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="G10" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H10" s="3"/>
     </row>
@@ -1208,20 +1200,22 @@
         <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F11" s="1"/>
+        <v>76</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="G11" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H11" s="3"/>
     </row>
@@ -1230,22 +1224,22 @@
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H12" s="3"/>
     </row>
@@ -1254,23 +1248,23 @@
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -1278,20 +1272,22 @@
         <v>10</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F14" s="1"/>
+        <v>61</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>61</v>
+      </c>
       <c r="G14" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H14" s="3"/>
     </row>
@@ -1300,23 +1296,25 @@
         <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F15" s="1"/>
+        <v>64</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="G15" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -1324,7 +1322,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>8</v>
@@ -1336,7 +1334,7 @@
         <v>10</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -1344,7 +1342,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>9</v>
@@ -1358,7 +1356,7 @@
         <v>10</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -1366,21 +1364,23 @@
         <v>14</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" s="1"/>
+        <v>133</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>134</v>
+      </c>
       <c r="F18" s="1"/>
       <c r="G18" s="2" t="s">
         <v>10</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -1388,21 +1388,23 @@
         <v>15</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="1"/>
+        <v>132</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>135</v>
+      </c>
       <c r="F19" s="1"/>
       <c r="G19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -1410,18 +1412,22 @@
         <v>16</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
+        <v>131</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>136</v>
+      </c>
       <c r="G20" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H20" s="3"/>
     </row>
@@ -1430,18 +1436,22 @@
         <v>17</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
+        <v>130</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>137</v>
+      </c>
       <c r="G21" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H21" s="3"/>
     </row>
@@ -1450,18 +1460,22 @@
         <v>18</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
+        <v>129</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="G22" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H22" s="3"/>
     </row>
@@ -1470,41 +1484,47 @@
         <v>19</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="H23" s="3"/>
     </row>
-    <row r="24" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>20</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E24" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>127</v>
+      </c>
       <c r="F24" s="1"/>
       <c r="G24" s="2" t="s">
         <v>10</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -1512,23 +1532,23 @@
         <v>21</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="2" t="s">
         <v>10</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -1536,22 +1556,22 @@
         <v>22</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H26" s="3"/>
     </row>
@@ -1560,23 +1580,23 @@
         <v>23</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="2" t="s">
         <v>10</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -1584,23 +1604,23 @@
         <v>24</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="2" t="s">
         <v>10</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -1608,16 +1628,16 @@
         <v>25</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H29" s="3"/>
     </row>
@@ -1626,7 +1646,7 @@
         <v>26</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -1640,16 +1660,16 @@
         <v>27</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H31" s="3"/>
     </row>
@@ -1658,7 +1678,7 @@
         <v>28</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -1672,25 +1692,25 @@
         <v>29</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>10</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -1698,51 +1718,37 @@
         <v>30</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H34" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G32">
-    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="PTE">
+  <conditionalFormatting sqref="G2:G34">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="6" operator="containsText" text="BL">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="BL">
       <formula>NOT(ISERROR(SEARCH("BL",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="KO">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="KO">
       <formula>NOT(ISERROR(SEARCH("KO",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="8" operator="containsText" text="OK">
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",G2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G33:G34">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
-      <formula>NOT(ISERROR(SEARCH("PTE",G33)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="BL">
-      <formula>NOT(ISERROR(SEARCH("BL",G33)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="KO">
-      <formula>NOT(ISERROR(SEARCH("KO",G33)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="OK">
-      <formula>NOT(ISERROR(SEARCH("OK",G33)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
